--- a/output/datastream_RI_latest.xlsx
+++ b/output/datastream_RI_latest.xlsx
@@ -13631,64 +13631,64 @@
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B322" t="n">
-        <v>161.95</v>
+        <v>166.9</v>
       </c>
       <c r="C322" t="n">
-        <v>265.79</v>
+        <v>268.88</v>
       </c>
       <c r="D322" t="n">
-        <v>105.18</v>
+        <v>105.56</v>
       </c>
       <c r="E322" t="n">
-        <v>354.58</v>
+        <v>361.23</v>
       </c>
       <c r="F322" t="n">
-        <v>631.21</v>
+        <v>599.34</v>
       </c>
       <c r="G322" t="n">
-        <v>273.93</v>
+        <v>270.83</v>
       </c>
       <c r="H322" t="n">
-        <v>148.63</v>
+        <v>149.18</v>
       </c>
       <c r="I322" t="n">
-        <v>496.88</v>
+        <v>510.85</v>
       </c>
       <c r="J322" t="n">
-        <v>275.95</v>
+        <v>277.37</v>
       </c>
       <c r="K322" t="n">
-        <v>174.35</v>
+        <v>178.07</v>
       </c>
       <c r="L322" t="n">
-        <v>1133.08</v>
+        <v>1122.82</v>
       </c>
       <c r="M322" t="n">
-        <v>838011.2</v>
+        <v>842018.6</v>
       </c>
       <c r="N322" t="n">
-        <v>134.25</v>
+        <v>133.94</v>
       </c>
       <c r="O322" t="n">
-        <v>171.17</v>
+        <v>171.65</v>
       </c>
       <c r="P322" t="n">
-        <v>273.21</v>
+        <v>271.82</v>
       </c>
       <c r="Q322" t="n">
-        <v>195.58</v>
+        <v>195.83</v>
       </c>
       <c r="R322" t="n">
-        <v>117.12</v>
+        <v>119.38</v>
       </c>
       <c r="S322" t="n">
-        <v>291.51</v>
+        <v>290.52</v>
       </c>
       <c r="T322" t="n">
-        <v>164.36</v>
+        <v>183.36</v>
       </c>
     </row>
   </sheetData>
@@ -14305,7 +14305,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>164.36</v>
+        <v>183.36</v>
       </c>
     </row>
     <row r="35">
@@ -20083,7 +20083,7 @@
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>838011.2</v>
+        <v>842018.6</v>
       </c>
     </row>
     <row r="356">
@@ -20821,7 +20821,7 @@
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>174.35</v>
+        <v>178.07</v>
       </c>
     </row>
     <row r="397">
@@ -23035,7 +23035,7 @@
     </row>
     <row r="519">
       <c r="A519" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>291.51</v>
+        <v>290.52</v>
       </c>
     </row>
     <row r="520">
@@ -26185,7 +26185,7 @@
     </row>
     <row r="694">
       <c r="A694" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         </is>
       </c>
       <c r="D694" t="n">
-        <v>148.63</v>
+        <v>149.18</v>
       </c>
     </row>
     <row r="695">
@@ -27931,7 +27931,7 @@
     </row>
     <row r="791">
       <c r="A791" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         </is>
       </c>
       <c r="D791" t="n">
-        <v>105.18</v>
+        <v>105.56</v>
       </c>
     </row>
     <row r="792">
@@ -30505,7 +30505,7 @@
     </row>
     <row r="934">
       <c r="A934" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B934" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         </is>
       </c>
       <c r="D934" t="n">
-        <v>354.58</v>
+        <v>361.23</v>
       </c>
     </row>
     <row r="935">
@@ -30883,7 +30883,7 @@
     </row>
     <row r="955">
       <c r="A955" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B955" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         </is>
       </c>
       <c r="D955" t="n">
-        <v>161.95</v>
+        <v>166.9</v>
       </c>
     </row>
     <row r="956">
@@ -32287,7 +32287,7 @@
     </row>
     <row r="1033">
       <c r="A1033" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         </is>
       </c>
       <c r="D1033" t="n">
-        <v>273.21</v>
+        <v>271.82</v>
       </c>
     </row>
     <row r="1034">
@@ -33637,7 +33637,7 @@
     </row>
     <row r="1108">
       <c r="A1108" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         </is>
       </c>
       <c r="D1108" t="n">
-        <v>265.79</v>
+        <v>268.88</v>
       </c>
     </row>
     <row r="1109">
@@ -34069,7 +34069,7 @@
     </row>
     <row r="1132">
       <c r="A1132" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         </is>
       </c>
       <c r="D1132" t="n">
-        <v>171.17</v>
+        <v>171.65</v>
       </c>
     </row>
     <row r="1133">
@@ -38335,7 +38335,7 @@
     </row>
     <row r="1369">
       <c r="A1369" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         </is>
       </c>
       <c r="D1369" t="n">
-        <v>273.93</v>
+        <v>270.83</v>
       </c>
     </row>
     <row r="1370">
@@ -41431,7 +41431,7 @@
     </row>
     <row r="1541">
       <c r="A1541" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B1541" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         </is>
       </c>
       <c r="D1541" t="n">
-        <v>195.58</v>
+        <v>195.83</v>
       </c>
     </row>
     <row r="1542">
@@ -47209,7 +47209,7 @@
     </row>
     <row r="1862">
       <c r="A1862" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B1862" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         </is>
       </c>
       <c r="D1862" t="n">
-        <v>1133.08</v>
+        <v>1122.82</v>
       </c>
     </row>
     <row r="1863">
@@ -51979,7 +51979,7 @@
     </row>
     <row r="2127">
       <c r="A2127" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B2127" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         </is>
       </c>
       <c r="D2127" t="n">
-        <v>631.21</v>
+        <v>599.34</v>
       </c>
     </row>
     <row r="2128">
@@ -56749,7 +56749,7 @@
     </row>
     <row r="2392">
       <c r="A2392" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B2392" t="inlineStr">
         <is>
@@ -56762,7 +56762,7 @@
         </is>
       </c>
       <c r="D2392" t="n">
-        <v>496.88</v>
+        <v>510.85</v>
       </c>
     </row>
     <row r="2393">
@@ -59107,7 +59107,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B2523" t="inlineStr">
         <is>
@@ -59120,7 +59120,7 @@
         </is>
       </c>
       <c r="D2523" t="n">
-        <v>134.25</v>
+        <v>133.94</v>
       </c>
     </row>
     <row r="2524">
@@ -60457,7 +60457,7 @@
     </row>
     <row r="2598">
       <c r="A2598" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B2598" t="inlineStr">
         <is>
@@ -60470,7 +60470,7 @@
         </is>
       </c>
       <c r="D2598" t="n">
-        <v>117.12</v>
+        <v>119.38</v>
       </c>
     </row>
     <row r="2599">
@@ -62887,7 +62887,7 @@
     </row>
     <row r="2733">
       <c r="A2733" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B2733" t="inlineStr">
         <is>
@@ -62900,7 +62900,7 @@
         </is>
       </c>
       <c r="D2733" t="n">
-        <v>275.95</v>
+        <v>277.37</v>
       </c>
     </row>
   </sheetData>
